--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marjory/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.vaillant.GPHUB\Documents\GPMLM\SDDEP\Stage\Stage 2026\Travail\DN Poissons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7DFCDF-A07A-AC43-ACEF-459BC1510750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E33EC45-C368-4078-8404-C760B5843607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-6630" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Declaration" sheetId="1" r:id="rId1"/>
@@ -1063,34 +1063,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5" customWidth="1"/>
-    <col min="3" max="3" width="48.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" customWidth="1"/>
+    <col min="3" max="3" width="48.81640625" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" customWidth="1"/>
+    <col min="5" max="5" width="18.6328125" customWidth="1"/>
+    <col min="6" max="6" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.6328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="32" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32" customWidth="1"/>
     <col min="19" max="19" width="28" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.1640625" customWidth="1"/>
+    <col min="20" max="20" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>81.84</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C3" t="str">
         <f>IF(B3&lt;&gt;"",VLOOKUP(B3,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1304,7 +1304,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C4" t="str">
         <f>IF(B4&lt;&gt;"",VLOOKUP(B4,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C5" t="str">
         <f>IF(B5&lt;&gt;"",VLOOKUP(B5,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C6" t="str">
         <f>IF(B6&lt;&gt;"",VLOOKUP(B6,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1499,7 +1499,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C7" t="str">
         <f>IF(B7&lt;&gt;"",VLOOKUP(B7,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1564,7 +1564,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C8" t="str">
         <f>IF(B8&lt;&gt;"",VLOOKUP(B8,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C9" t="str">
         <f>IF(B9&lt;&gt;"",VLOOKUP(B9,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1694,7 +1694,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C10" t="str">
         <f>IF(B10&lt;&gt;"",VLOOKUP(B10,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1759,7 +1759,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C11" t="str">
         <f>IF(B11&lt;&gt;"",VLOOKUP(B11,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1824,7 +1824,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C12" t="str">
         <f>IF(B12&lt;&gt;"",VLOOKUP(B12,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1889,7 +1889,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C13" t="str">
         <f>IF(B13&lt;&gt;"",VLOOKUP(B13,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -1954,7 +1954,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C14" t="str">
         <f>IF(B14&lt;&gt;"",VLOOKUP(B14,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2019,7 +2019,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C15" t="str">
         <f>IF(B15&lt;&gt;"",VLOOKUP(B15,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2084,7 +2084,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C16" t="str">
         <f>IF(B16&lt;&gt;"",VLOOKUP(B16,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C17" t="str">
         <f>IF(B17&lt;&gt;"",VLOOKUP(B17,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2214,7 +2214,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C18" t="str">
         <f>IF(B18&lt;&gt;"",VLOOKUP(B18,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C19" t="str">
         <f>IF(B19&lt;&gt;"",VLOOKUP(B19,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2344,7 +2344,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C20" t="str">
         <f>IF(B20&lt;&gt;"",VLOOKUP(B20,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2409,7 +2409,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C21" t="str">
         <f>IF(B21&lt;&gt;"",VLOOKUP(B21,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2474,7 +2474,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C22" t="str">
         <f>IF(B22&lt;&gt;"",VLOOKUP(B22,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2539,7 +2539,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C23" t="str">
         <f>IF(B23&lt;&gt;"",VLOOKUP(B23,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2604,7 +2604,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C24" t="str">
         <f>IF(B24&lt;&gt;"",VLOOKUP(B24,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2669,7 +2669,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C25" t="str">
         <f>IF(B25&lt;&gt;"",VLOOKUP(B25,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2734,7 +2734,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C26" t="str">
         <f>IF(B26&lt;&gt;"",VLOOKUP(B26,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2799,7 +2799,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C27" t="str">
         <f>IF(B27&lt;&gt;"",VLOOKUP(B27,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2864,7 +2864,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C28" t="str">
         <f>IF(B28&lt;&gt;"",VLOOKUP(B28,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2929,7 +2929,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C29" t="str">
         <f>IF(B29&lt;&gt;"",VLOOKUP(B29,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -2994,7 +2994,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C30" t="str">
         <f>IF(B30&lt;&gt;"",VLOOKUP(B30,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3059,7 +3059,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C31" t="str">
         <f>IF(B31&lt;&gt;"",VLOOKUP(B31,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3124,7 +3124,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C32" t="str">
         <f>IF(B32&lt;&gt;"",VLOOKUP(B32,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3189,7 +3189,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C33" t="str">
         <f>IF(B33&lt;&gt;"",VLOOKUP(B33,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C34" t="str">
         <f>IF(B34&lt;&gt;"",VLOOKUP(B34,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3319,7 +3319,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C35" t="str">
         <f>IF(B35&lt;&gt;"",VLOOKUP(B35,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3384,7 +3384,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C36" t="str">
         <f>IF(B36&lt;&gt;"",VLOOKUP(B36,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3449,7 +3449,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C37" t="str">
         <f>IF(B37&lt;&gt;"",VLOOKUP(B37,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3514,7 +3514,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C38" t="str">
         <f>IF(B38&lt;&gt;"",VLOOKUP(B38,Tableau3[#All],2,0),"")</f>
         <v/>
@@ -3603,16 +3603,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED48872-91E8-49A7-BF70-883F96B227DE}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="26.5" customWidth="1"/>
-    <col min="5" max="5" width="19.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.6328125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="3" max="3" width="27.453125" customWidth="1"/>
+    <col min="4" max="4" width="26.453125" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>25</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>34</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>34</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>34</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>34</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>34</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>41</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="14"/>
       <c r="B15" s="14" t="s">
         <v>53</v>
@@ -3884,13 +3884,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB195B26-F7E2-4470-95CE-93C18E346372}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" customWidth="1"/>
-    <col min="2" max="2" width="74.5" customWidth="1"/>
+    <col min="1" max="1" width="18.36328125" customWidth="1"/>
+    <col min="2" max="2" width="74.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>47</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>51</v>
       </c>

--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.vaillant.GPHUB\Documents\GPMLM\SDDEP\Stage\Stage 2026\Travail\DN Poissons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E33EC45-C368-4078-8404-C760B5843607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20541ACA-77A9-49C9-975D-A0B2E877435B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-6630" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-6720" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Declaration" sheetId="1" r:id="rId1"/>
@@ -241,17 +241,20 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -274,7 +277,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -403,19 +406,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="1" tint="0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color theme="1" tint="0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -424,7 +414,9 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -449,7 +441,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3698,20 +3690,18 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="13">
-        <v>18.7</v>
-      </c>
-      <c r="D6" s="13">
-        <v>5.45</v>
-      </c>
-      <c r="E6" s="13">
-        <v>2.5</v>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="7">
+        <v>15</v>
+      </c>
+      <c r="D6" s="14">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="E6" s="15">
+        <v>1.85</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -3719,16 +3709,16 @@
         <v>34</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="13">
-        <v>17.8</v>
+        <v>18.7</v>
       </c>
       <c r="D7" s="13">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="E7" s="13">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3736,16 +3726,16 @@
         <v>34</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="C8" s="13">
+        <v>17.8</v>
+      </c>
+      <c r="D8" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="E8" s="13">
+        <v>1.97</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3753,33 +3743,33 @@
         <v>34</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D9" s="8">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="13">
-        <v>14.2</v>
-      </c>
-      <c r="D10" s="13">
-        <v>4.57</v>
-      </c>
-      <c r="E10" s="13">
-        <v>2.13</v>
+        <v>40</v>
+      </c>
+      <c r="C10" s="8">
+        <v>14</v>
+      </c>
+      <c r="D10" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -3787,16 +3777,16 @@
         <v>41</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="8">
-        <v>17</v>
-      </c>
-      <c r="D11" s="8">
-        <v>4.8</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.15</v>
+        <v>42</v>
+      </c>
+      <c r="C11" s="13">
+        <v>14.2</v>
+      </c>
+      <c r="D11" s="13">
+        <v>4.57</v>
+      </c>
+      <c r="E11" s="13">
+        <v>2.13</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -3804,16 +3794,16 @@
         <v>41</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="8">
-        <v>18.77</v>
+        <v>17</v>
       </c>
       <c r="D12" s="8">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="E12" s="8">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3821,48 +3811,50 @@
         <v>41</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="8">
+        <v>18.77</v>
+      </c>
+      <c r="D13" s="8">
+        <v>5.25</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C14" s="8">
         <v>16.809999999999999</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D14" s="8">
         <v>5.2</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E14" s="8">
         <v>2.31</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C15" s="11">
         <v>13.9</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D15" s="9">
         <v>4.7</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E15" s="10">
         <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="14">
-        <v>15</v>
-      </c>
-      <c r="D15" s="15">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="E15" s="14">
-        <v>1.85</v>
       </c>
     </row>
   </sheetData>
@@ -3870,11 +3862,14 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A15" xr:uid="{E2910900-9C30-4A18-9496-476E3FB8CC0C}">
       <formula1>"DSK Fish,Poissonnerie Bapte,Delta Transit"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B14" xr:uid="{9CBFDF41-04DC-4A2C-BFA5-AF229712E91E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B15" xr:uid="{9CBFDF41-04DC-4A2C-BFA5-AF229712E91E}">
       <formula1>"LA DIOSA,PATHFINDER,NATHALIA,SAMANTHA DEL VALLEE,ARACELYS MARIA,EL SUR,DON CRUZ,QUEEN MARY,MARIA CELIS 3,MARIA CELIS 2,MARIA CELIS 4,MAYELEWO,EL SUR,DON FAUSTINO"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="B6" listDataValidation="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Book 1.xlsx
+++ b/Book 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.vaillant.GPHUB\Documents\GPMLM\SDDEP\Stage\Stage 2026\Travail\DN Poissons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20541ACA-77A9-49C9-975D-A0B2E877435B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00FF74E-1758-47F1-B56C-5E4BF3D2929C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-6720" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Declaration" sheetId="1" r:id="rId1"/>
